--- a/tests/protocols/fixtures/lauf/sarah.xlsx
+++ b/tests/protocols/fixtures/lauf/sarah.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -530,74 +530,74 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Geburtsjahr</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1988</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Vierstellig, z.B. 1985</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Geschlecht</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
+          <t>Geburtsjahr</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1988</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>m | w | d (optional)</t>
+          <t>Vierstellig, z.B. 1985</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Gewicht (kg)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>44</v>
+          <t>Geschlecht</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>m | w | d (optional)</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Größe (m)</t>
+          <t>Gewicht (kg)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>In Metern, z.B. 1.79</t>
-        </is>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Trainingsziel</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n"/>
+          <t>Größe (m)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>In Metern, z.B. 1.79</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Wettkampfziel</t>
+          <t>Trainingsziel</t>
         </is>
       </c>
       <c r="B10" s="3" t="n"/>
@@ -605,7 +605,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Trainingsumfang/Woche</t>
+          <t>Wettkampfziel</t>
         </is>
       </c>
       <c r="B11" s="3" t="n"/>
@@ -613,10 +613,18 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Trainingsumfang/Woche</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Leistungsniveau</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -629,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -727,7 +735,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Anfangsintensität</t>
+          <t>Anfangsbelastung</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -843,6 +851,20 @@
       <c r="C14" s="4" t="inlineStr">
         <is>
           <t>JA oder NEIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nachbelastungslaktat 3min (mmol/l)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Nachbelastungslaktat 5min (mmol/l)</t>
         </is>
       </c>
     </row>

--- a/tests/protocols/fixtures/lauf/sarah.xlsx
+++ b/tests/protocols/fixtures/lauf/sarah.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -491,113 +491,103 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sportart</t>
+          <t>Vorname</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Lauf</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Erlaubt: lauf | rad | triathlon-rad | triathlon-lauf | unspezifisch</t>
+          <t>Sarah</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Vorname</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Seckendorf</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Seckendorf</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Geburtsjahr</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1988</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Vierstellig, z.B. 1985</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Geburtsjahr</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>1988</v>
+          <t>Geschlecht</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Vierstellig, z.B. 1985</t>
+          <t>m | w | d (optional)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Geschlecht</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>m | w | d (optional)</t>
-        </is>
+          <t>Gewicht (kg)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Gewicht (kg)</t>
+          <t>Größe (m)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>44</v>
+        <v>1.54</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>In Metern, z.B. 1.79</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Größe (m)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>In Metern, z.B. 1.79</t>
-        </is>
-      </c>
+          <t>Trainingsziel</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Trainingsziel</t>
+          <t>Wettkampfziel</t>
         </is>
       </c>
       <c r="B10" s="3" t="n"/>
@@ -605,7 +595,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Wettkampfziel</t>
+          <t>Trainingsumfang/Woche</t>
         </is>
       </c>
       <c r="B11" s="3" t="n"/>
@@ -613,18 +603,10 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Trainingsumfang/Woche</t>
+          <t>Leistungsniveau</t>
         </is>
       </c>
       <c r="B12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Leistungsniveau</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -637,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -663,206 +645,223 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Testdatum</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>23.05.2024</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Format: TT.MM.JJJJ</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sportart</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Lauf</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Erlaubt: lauf | rad | triathlon-rad | triathlon-lauf | unspezifisch</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Uhrzeit</t>
+          <t>Testdatum</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>23.05.2024</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Format: HH:MM</t>
+          <t>Format: TT.MM.JJJJ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Durchführungsort</t>
+          <t>Uhrzeit</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Laufcamp Achensee</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Format: HH:MM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Testleiter</t>
+          <t>Durchführungsort</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Anna-Maria Wörndle</t>
+          <t>Laufcamp Achensee</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Gerät</t>
+          <t>Testleiter</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Laufband Atoll Achensee</t>
+          <t>Anna-Maria Wörndle</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Anfangsbelastung</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>km/h (Lauf) | W (Rad) | Stufe (Unspez)</t>
+          <t>Gerät</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Laufband Atoll Achensee</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Stufeninkrement</t>
+          <t>Anfangsbelastung</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>km/h | W | Stufen</t>
+          <t>km/h (Lauf) | W (Rad) | Stufe (Unspez)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Stufendauer (min)</t>
+          <t>Stufeninkrement</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Minuten</t>
+          <t>km/h | W | Stufen</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Stufenlänge (m)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n"/>
+          <t>Stufendauer (min)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Optional, nur Lauf (z.B. 1600)</t>
+          <t>Minuten</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Besonderheiten</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>1% Steigung</t>
-        </is>
-      </c>
+          <t>Stufenlänge (m)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Freitext</t>
+          <t>Optional, nur Lauf (z.B. 1600)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Letzte Stufe vollständig absolviert</t>
+          <t>Besonderheiten</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>1% Steigung</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>JA oder NEIN</t>
+          <t>Freitext</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Dauer letzte Stufe (min)</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
+          <t>Letzte Stufe vollständig absolviert</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Nur ausfüllen wenn NEIN oben</t>
+          <t>JA oder NEIN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Dauer letzte Stufe (min)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Nur ausfüllen wenn NEIN oben</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Ausbelastung</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>JA oder NEIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Nachbelastungslaktat 3min (mmol/l)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>Nachbelastungslaktat 3min (mmol/l)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Nachbelastungslaktat 5min (mmol/l)</t>
         </is>
@@ -935,7 +934,7 @@
         <v>1.7</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -952,7 +951,7 @@
         <v>1.8</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -969,7 +968,7 @@
         <v>1.8</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -986,7 +985,7 @@
         <v>2.8</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -1003,7 +1002,7 @@
         <v>4.3</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -1020,7 +1019,7 @@
         <v>6.6</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
